--- a/자료/navi/네비게이토_구절입력_73.xlsx
+++ b/자료/navi/네비게이토_구절입력_73.xlsx
@@ -2,47 +2,80 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28690" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구절 입력" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="001A3A6B"/>
+      <color rgb="FF1A3A6B"/>
       <sz val="18"/>
     </font>
     <font>
-      <color rgb="004A5560"/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF4A5560"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="001A3A6B"/>
+      <color rgb="FF1A3A6B"/>
       <sz val="13"/>
     </font>
     <font>
-      <color rgb="001F2328"/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF1F2328"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -50,10 +83,10 @@
       <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
+      <color rgb="006B7280"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -62,26 +95,51 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A3A6B"/>
+        <fgColor rgb="FF1A3A6B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C3A253"/>
+        <fgColor rgb="FFC3A253"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF7F0"/>
+        <fgColor rgb="FFFAF7F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006B7280"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6E0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8D0BC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD8D0BC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD8D0BC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8D0BC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -102,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -140,15 +198,34 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFF6E0"/>
+          <fgColor rgb="FFFFF6E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF6E0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -515,13 +592,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:B19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="34.05" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>네비게이토 성경암송 — 본문 입력 양식(카드 73장)</t>
@@ -535,77 +612,77 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="19.5" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>채워 주실 것은 「구절 입력」 시트의 I열 「본문」 하나입니다</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="22.05" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>· 대한성서공회 성경 읽기(bible.bskorea.or.kr)에서 개역개정을 열어 그 절을 복사해 붙여 넣어 주세요.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
+    <row r="7" ht="22.05" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>· 절 번호 · 괄호 · 각주 표시는 빼 주세요. 두 절짜리 카드(예: 요일 5:11-12)는 한 칸에 띄어쓰기 하나로 이어 붙입니다.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="22.05" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>· 시 119:9, 11 처럼 가운데 절을 건너뛰는 카드는 9절 다음에 11절을 띄어쓰기 하나로 이어 붙입니다.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="22.05" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>· J열 「글자 수」 · K열 「확인」은 저절로 채워집니다. 본문이 빈 줄은 노란색으로 보입니다.</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="19.5" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>함께 확인해 주실 것(카드 실물이 있으면)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
+    <row r="12" ht="22.05" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>· 생활 지침 8구절의 주제 이름(E열)이 비어 있습니다 — 카드에 적힌 이름을 넣어 주세요.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="22.05" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
           <t>· 카드 번호(F열)는 자료마다 매기는 법이 달라 「A-1 ~ A-12」처럼 절마다 붙여 두었습니다. 카드와 다르면 고쳐 주세요.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="22.05" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
           <t>· 5확신 · 생활 지침 8구절의 장절은 공식 원본과 대조하지 못했습니다. 카드와 다르면 G열을 고쳐 주세요.</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="19.5" customHeight="1">
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>바꾸면 안 되는 것</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="22.05" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
           <t>· B열 「번호」는 앱 진도의 열쇠입니다 — 고치지 마세요. 줄을 빼야 하면 지우지 말고 M열 메모에 「빼기」라고 적어 주세요.</t>
@@ -630,22 +707,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="12" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -691,7 +768,7 @@
       </c>
       <c r="I1" s="6" t="inlineStr">
         <is>
-          <t>본문(개역개정 — 붙여 넣기)</t>
+          <t>본문(개역개정 4판 — 대한성서공회 원문)</t>
         </is>
       </c>
       <c r="J1" s="5" t="inlineStr">
@@ -712,6 +789,16 @@
       <c r="M1" s="5" t="inlineStr">
         <is>
           <t>메모</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>처음 붙여 넣으신 본문(개역한글 · 참고)</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>개역개정으로 바뀜</t>
         </is>
       </c>
     </row>
@@ -752,7 +839,11 @@
           <t>요한일서 5장 11-12절</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>또 증거는 이것이니 하나님이 우리에게 영생을 주신 것과 이 생명이 그의 아들 안에 있는 그것이니라 아들이 있는 자에게는 생명이 있고 하나님의 아들이 없는 자에게는 생명이 없느니라</t>
+        </is>
+      </c>
       <c r="J2" s="7">
         <f>IF(I2="","",LEN(SUBSTITUTE(I2," ","")))</f>
         <v/>
@@ -761,8 +852,14 @@
         <f>IF(I2="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L2" s="10" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>또 증거는 이것이니 하나님이 우리에게 영생을 주신 것과 이 생명이 그의 아들 안에 있는 그것이니라 아들이 있는 자에게는 생명이 있고 하나님의 아들이 없는 자에게는 생명이 없느니라</t>
+        </is>
+      </c>
+      <c r="O2" s="15" t="inlineStr"/>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="7" t="n">
@@ -801,7 +898,11 @@
           <t>요한복음 16장 24절</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr"/>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>지금까지는 너희가 내 이름으로 아무 것도 구하지 아니하였으나 구하라 그리하면 받으리니 너희 기쁨이 충만하리라</t>
+        </is>
+      </c>
       <c r="J3" s="7">
         <f>IF(I3="","",LEN(SUBSTITUTE(I3," ","")))</f>
         <v/>
@@ -810,8 +911,14 @@
         <f>IF(I3="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L3" s="10" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="14" t="inlineStr">
+        <is>
+          <t>지금까지는 너희가 내 이름으로 아무것도 구하지 아니하였으나 구하라 그리하면 받으리니 너희 기쁨이 충만하리라</t>
+        </is>
+      </c>
+      <c r="O3" s="15" t="inlineStr"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="7" t="n">
@@ -850,7 +957,11 @@
           <t>고린도전서 10장 13절</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>사람이 감당할 시험 밖에는 너희가 당한 것이 없나니 오직 하나님은 미쁘사 너희가 감당하지 못할 시험 당함을 허락하지 아니하시고 시험 당할 즈음에 또한 피할 길을 내사 너희로 능히 감당하게 하시느니라</t>
+        </is>
+      </c>
       <c r="J4" s="7">
         <f>IF(I4="","",LEN(SUBSTITUTE(I4," ","")))</f>
         <v/>
@@ -859,8 +970,18 @@
         <f>IF(I4="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L4" s="10" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>사람이 감당할 시험 밖에는 너희에게 당한 것이 없나니 오직 하나님은 미쁘사 너희가 감당치 못할 시험 당함을 허락지 아니하시고 시험 당할 즈음에 또한 피할 길을 내사 너희로 능히 감당하게 하시느니라</t>
+        </is>
+      </c>
+      <c r="O4" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="7" t="n">
@@ -899,7 +1020,11 @@
           <t>요한일서 1장 9절</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>만일 우리가 우리 죄를 자백하면 그는 미쁘시고 의로우사 우리 죄를 사하시며 우리를 모든 불의에서 깨끗하게 하실 것이요</t>
+        </is>
+      </c>
       <c r="J5" s="7">
         <f>IF(I5="","",LEN(SUBSTITUTE(I5," ","")))</f>
         <v/>
@@ -908,8 +1033,18 @@
         <f>IF(I5="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L5" s="10" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="14" t="inlineStr">
+        <is>
+          <t>만일 우리가 우리 죄를 자백하면 저는 미쁘시고 의로우사 우리 죄를 사하시며 모든 불의에서 우리를 깨끗케 하실 것이요</t>
+        </is>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="7" t="n">
@@ -948,7 +1083,11 @@
           <t>잠언 3장 5-6절</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>너는 마음을 다하여 여호와를 신뢰하고 네 명철을 의지하지 말라 너는 범사에 그를 인정하라 그리하면 네 길을 지도하시리라</t>
+        </is>
+      </c>
       <c r="J6" s="7">
         <f>IF(I6="","",LEN(SUBSTITUTE(I6," ","")))</f>
         <v/>
@@ -957,8 +1096,18 @@
         <f>IF(I6="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L6" s="10" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="14" t="inlineStr">
+        <is>
+          <t>너는 마음을 다하여 여호와를 의뢰하고 네 명철을 의지하지 말라 너는 범사에 그를 인정하라 그리하면 네 길을 지도하시리라</t>
+        </is>
+      </c>
+      <c r="O6" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="7" t="n">
@@ -977,7 +1126,11 @@
           <t>그리스도인의 생활 지침</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>그리스도 안의 생활</t>
+        </is>
+      </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>지침-1</t>
@@ -993,7 +1146,11 @@
           <t>요한복음 15장 5절</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>나는 포도나무요 너희는 가지라 그가 내 안에, 내가 그 안에 거하면 사람이 열매를 많이 맺나니 나를 떠나서는 너희가 아무 것도 할 수 없음이라</t>
+        </is>
+      </c>
       <c r="J7" s="7">
         <f>IF(I7="","",LEN(SUBSTITUTE(I7," ","")))</f>
         <v/>
@@ -1002,8 +1159,18 @@
         <f>IF(I7="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L7" s="10" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="14" t="inlineStr">
+        <is>
+          <t>나는 포도나무요 너희는 가지니 저가 내 안에 내가 저 안에 있으면 이 사람은 과실을 많이 맺나니 나를 떠나서는 너희가 아무것도 할 수 없음이라</t>
+        </is>
+      </c>
+      <c r="O7" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -1022,7 +1189,11 @@
           <t>그리스도인의 생활 지침</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>하나님의 말씀에 의한 생활</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
           <t>지침-2</t>
@@ -1038,7 +1209,11 @@
           <t>사도행전 20장 32절</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>지금 내가 여러분을 주와 및 그 은혜의 말씀에 부탁하노니 그 말씀이 여러분을 능히 든든히 세우사 거룩하게 하심을 입은 모든 자 가운데 기업이 있게 하시리라</t>
+        </is>
+      </c>
       <c r="J8" s="7">
         <f>IF(I8="","",LEN(SUBSTITUTE(I8," ","")))</f>
         <v/>
@@ -1047,8 +1222,18 @@
         <f>IF(I8="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L8" s="10" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>지금 내가 너희를 주와 및 그 은혜의 말씀께 부탁하노니 그 말씀이 너희를 능히 든든히 세우사 거룩케 하심을 입은 모든 자 가운데 기업이 있게 하시리라</t>
+        </is>
+      </c>
+      <c r="O8" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="n">
@@ -1067,7 +1252,11 @@
           <t>그리스도인의 생활 지침</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>하나님의 성령에 의한 생활</t>
+        </is>
+      </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>지침-3</t>
@@ -1083,7 +1272,11 @@
           <t>로마서 8장 14절</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>무릇 하나님의 영으로 인도함을 받는 사람은 곧 하나님의 아들이라</t>
+        </is>
+      </c>
       <c r="J9" s="7">
         <f>IF(I9="","",LEN(SUBSTITUTE(I9," ","")))</f>
         <v/>
@@ -1092,8 +1285,18 @@
         <f>IF(I9="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L9" s="10" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="14" t="inlineStr">
+        <is>
+          <t>무릇 하나님의 영으로 인도함을 받는 그들은 곧 하나님의 아들이라</t>
+        </is>
+      </c>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -1112,7 +1315,11 @@
           <t>그리스도인의 생활 지침</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>믿음에 의한 생활</t>
+        </is>
+      </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>지침-4</t>
@@ -1128,7 +1335,11 @@
           <t>고린도후서 5장 7절</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>이는 우리가 믿음으로 행하고 보는 것으로 행하지 아니함이로라</t>
+        </is>
+      </c>
       <c r="J10" s="7">
         <f>IF(I10="","",LEN(SUBSTITUTE(I10," ","")))</f>
         <v/>
@@ -1137,8 +1348,18 @@
         <f>IF(I10="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L10" s="10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>이는 우리가 믿음으로 행하고 보는 것으로 하지 아니함이로라</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="n">
@@ -1157,7 +1378,11 @@
           <t>그리스도인의 생활 지침</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>사랑에 의한 생활</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>지침-5</t>
@@ -1173,7 +1398,11 @@
           <t>요한일서 4장 11절</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>사랑하는 자들아 하나님이 이같이 우리를 사랑하셨은즉 우리도 서로 사랑하는 것이 마땅하도다</t>
+        </is>
+      </c>
       <c r="J11" s="7">
         <f>IF(I11="","",LEN(SUBSTITUTE(I11," ","")))</f>
         <v/>
@@ -1182,8 +1411,14 @@
         <f>IF(I11="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L11" s="10" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="14" t="inlineStr">
+        <is>
+          <t>사랑하는 자들아 하나님이 이같이 우리를 사랑하셨은즉 우리도 서로 사랑하는 것이 마땅하도다</t>
+        </is>
+      </c>
+      <c r="O11" s="15" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -1202,7 +1437,11 @@
           <t>그리스도인의 생활 지침</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr"/>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>그리스도인의 교제하는 생활</t>
+        </is>
+      </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
           <t>지침-6</t>
@@ -1218,7 +1457,11 @@
           <t>요한일서 1장 7절</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>그가 빛 가운데 계신 것 같이 우리도 빛 가운데 행하면 우리가 서로 사귐이 있고 그 아들 예수의 피가 우리를 모든 죄에서 깨끗하게 하실 것이요</t>
+        </is>
+      </c>
       <c r="J12" s="7">
         <f>IF(I12="","",LEN(SUBSTITUTE(I12," ","")))</f>
         <v/>
@@ -1227,8 +1470,18 @@
         <f>IF(I12="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L12" s="10" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t>저가 빛 가운데 계신 것같이 우리도 빛 가운데 행하면 우리가 서로 사귐이 있고 그 아들 예수의 피가 우리를 모든 죄에서 깨끗하게 하실 것이요</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="7" t="n">
@@ -1247,7 +1500,11 @@
           <t>그리스도인의 생활 지침</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>증인으로서의 생활</t>
+        </is>
+      </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>지침-7</t>
@@ -1263,7 +1520,11 @@
           <t>베드로전서 3장 15절</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>너희 마음에 그리스도를 주로 삼아 거룩하게 하고 너희 속에 있는 소망에 관한 이유를 묻는 자에게는 대답할 것을 항상 준비하되 온유와 두려움으로 하고</t>
+        </is>
+      </c>
       <c r="J13" s="7">
         <f>IF(I13="","",LEN(SUBSTITUTE(I13," ","")))</f>
         <v/>
@@ -1272,8 +1533,18 @@
         <f>IF(I13="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L13" s="10" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <t>너희 마음에 그리스도를 주로 삼아 거룩하게 하고 너희 속에 있는 소망에 관한 이유를 묻는 자에게는 대답할 것을 항상 예비하되 온유와 두려움으로 하고</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -1292,7 +1563,11 @@
           <t>그리스도인의 생활 지침</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>후히 드리는 생활</t>
+        </is>
+      </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
           <t>지침-8</t>
@@ -1308,7 +1583,11 @@
           <t>고린도후서 9장 7절</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr"/>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>각각 그 마음에 정한 대로 할 것이요 인색함으로나 억지로 하지 말지니 하나님은 즐겨 내는 자를 사랑하시느니라</t>
+        </is>
+      </c>
       <c r="J14" s="7">
         <f>IF(I14="","",LEN(SUBSTITUTE(I14," ","")))</f>
         <v/>
@@ -1317,8 +1596,14 @@
         <f>IF(I14="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L14" s="10" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t>각각 그 마음에 정한 대로 할 것이요 인색함으로나 억지로 하지 말지니 하나님은 즐겨 내는 자를 사랑하시느니라</t>
+        </is>
+      </c>
+      <c r="O14" s="15" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="7" t="n">
@@ -1357,7 +1642,11 @@
           <t>고린도후서 5장 17절</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>그런즉 누구든지 그리스도 안에 있으면 새로운 피조물이라 이전 것은 지나갔으니 보라 새 것이 되었도다</t>
+        </is>
+      </c>
       <c r="J15" s="7">
         <f>IF(I15="","",LEN(SUBSTITUTE(I15," ","")))</f>
         <v/>
@@ -1366,10 +1655,16 @@
         <f>IF(I15="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="42" customHeight="1">
+      <c r="L15" s="10" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="14" t="inlineStr">
+        <is>
+          <t>그런즉 누구든지 그리스도 안에 있으면 새로운 피조물이라 이전 것은 지나갔으니 보라 새 것이 되었도다</t>
+        </is>
+      </c>
+      <c r="O15" s="15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="70.5" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
@@ -1406,7 +1701,11 @@
           <t>갈라디아서 2장 20절</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>내가 그리스도와 함께 십자가에 못 박혔나니 그런즉 이제는 내가 사는 것이 아니요 오직 내 안에 그리스도께서 사시는 것이라 이제 내가 육체 가운데 사는 것은 나를 사랑하사 나를 위하여 자기 자신을 버리신 하나님의 아들을 믿는 믿음 안에서 사는 것이라</t>
+        </is>
+      </c>
       <c r="J16" s="7">
         <f>IF(I16="","",LEN(SUBSTITUTE(I16," ","")))</f>
         <v/>
@@ -1415,8 +1714,18 @@
         <f>IF(I16="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
+      <c r="L16" s="10" t="n"/>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="14" t="inlineStr">
+        <is>
+          <t>내가 그리스도와 함께 십자가에 못 박혔나니 그런즉 이제는 내가 산 것이 아니요 오직 내 안에 그리스도께서 사신 것이라 이제 내가 육체 가운데 사는 것은 나를 사랑하사 나를 위하여 자기 몸을 버리신 하나님의 아들을 믿는 믿음 안에서 사는 것이라</t>
+        </is>
+      </c>
+      <c r="O16" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="7" t="n">
@@ -1455,7 +1764,11 @@
           <t>로마서 12장 1절</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>그러므로 형제들아 내가 하나님의 모든 자비하심으로 너희를 권하노니 너희 몸을 하나님이 기뻐하시는 거룩한 산 제물로 드리라 이는 너희가 드릴 영적 예배니라</t>
+        </is>
+      </c>
       <c r="J17" s="7">
         <f>IF(I17="","",LEN(SUBSTITUTE(I17," ","")))</f>
         <v/>
@@ -1464,8 +1777,18 @@
         <f>IF(I17="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L17" s="10" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
+      <c r="L17" s="10" t="n"/>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="14" t="inlineStr">
+        <is>
+          <t>그러므로 형제들아 내가 하나님의 모든 자비하심으로 너희를 권하노니 너희 몸을 하나님이 기뻐하시는 거룩한 산 제사로 드리라 이는 너희의 드릴 영적 예배니라</t>
+        </is>
+      </c>
+      <c r="O17" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="7" t="n">
@@ -1504,7 +1827,11 @@
           <t>요한복음 14장 21절</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>나의 계명을 지키는 자라야 나를 사랑하는 자니 나를 사랑하는 자는 내 아버지께 사랑을 받을 것이요 나도 그를 사랑하여 그에게 나를 나타내리라</t>
+        </is>
+      </c>
       <c r="J18" s="7">
         <f>IF(I18="","",LEN(SUBSTITUTE(I18," ","")))</f>
         <v/>
@@ -1513,8 +1840,18 @@
         <f>IF(I18="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L18" s="10" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="14" t="inlineStr">
+        <is>
+          <t>나의 계명을 가지고 지키는 자라야 나를 사랑하는 자니 나를 사랑하는 자는 내 아버지께 사랑을 받을 것이요 나도 그를 사랑하여 그에게 나를 나타내리라</t>
+        </is>
+      </c>
+      <c r="O18" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="7" t="n">
@@ -1553,7 +1890,11 @@
           <t>디모데후서 3장 16절</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>모든 성경은 하나님의 감동으로 된 것으로 교훈과 책망과 바르게 함과 의로 교육하기에 유익하니</t>
+        </is>
+      </c>
       <c r="J19" s="7">
         <f>IF(I19="","",LEN(SUBSTITUTE(I19," ","")))</f>
         <v/>
@@ -1562,8 +1903,14 @@
         <f>IF(I19="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L19" s="10" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="14" t="inlineStr">
+        <is>
+          <t>모든 성경은 하나님의 감동으로 된 것으로 교훈과 책망과 바르게 함과 의로 교육하기에 유익하니</t>
+        </is>
+      </c>
+      <c r="O19" s="15" t="inlineStr"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -1602,7 +1949,11 @@
           <t>여호수아 1장 8절</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>이 율법책을 네 입에서 떠나지 말게 하며 주야로 그것을 묵상하여 그 안에 기록된 대로 다 지켜 행하라 그리하면 네 길이 평탄하게 될 것이며 네가 형통하리라</t>
+        </is>
+      </c>
       <c r="J20" s="7">
         <f>IF(I20="","",LEN(SUBSTITUTE(I20," ","")))</f>
         <v/>
@@ -1611,8 +1962,18 @@
         <f>IF(I20="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L20" s="10" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
+      <c r="L20" s="10" t="n"/>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="14" t="inlineStr">
+        <is>
+          <t>이 율법책을 네 입에서 떠나지 말게 하며 주야로 그것을 묵상하여 그 가운데 기록한대로 다 지켜 행하라 그리하면 네 길이 평탄하게 될 것이라 네가 형통하리라</t>
+        </is>
+      </c>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="7" t="n">
@@ -1651,7 +2012,11 @@
           <t>요한복음 15장 7절</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>너희가 내 안에 거하고 내 말이 너희 안에 거하면 무엇이든지 원하는 대로 구하라 그리하면 이루리라</t>
+        </is>
+      </c>
       <c r="J21" s="7">
         <f>IF(I21="","",LEN(SUBSTITUTE(I21," ","")))</f>
         <v/>
@@ -1660,8 +2025,14 @@
         <f>IF(I21="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L21" s="10" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="n"/>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="14" t="inlineStr">
+        <is>
+          <t>너희가 내 안에 거하고 내 말이 너희 안에 거하면 무엇이든지 원하는대로 구하라 그리하면 이루리라</t>
+        </is>
+      </c>
+      <c r="O21" s="15" t="inlineStr"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="7" t="n">
@@ -1700,7 +2071,11 @@
           <t>빌립보서 4장 6-7절</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr"/>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>아무 것도 염려하지 말고 다만 모든 일에 기도와 간구로, 너희 구할 것을 감사함으로 하나님께 아뢰라 그리하면 모든 지각에 뛰어난 하나님의 평강이 그리스도 예수 안에서 너희 마음과 생각을 지키시리라</t>
+        </is>
+      </c>
       <c r="J22" s="7">
         <f>IF(I22="","",LEN(SUBSTITUTE(I22," ","")))</f>
         <v/>
@@ -1709,8 +2084,18 @@
         <f>IF(I22="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L22" s="10" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
+      <c r="L22" s="10" t="n"/>
+      <c r="M22" s="10" t="n"/>
+      <c r="N22" s="14" t="inlineStr">
+        <is>
+          <t>아무 것도 염려하지 말고 오직 모든 일에 기도와 간구로 너희 구할 것을 감사함으로 하나님께 아뢰라 그리하면 모든 지각에 뛰어난 하나님의 평강이 그리스도 예수 안에서 너희 마음과 생각을 지키시리라</t>
+        </is>
+      </c>
+      <c r="O22" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="7" t="n">
@@ -1749,7 +2134,11 @@
           <t>마태복음 18장 20절</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>두세 사람이 내 이름으로 모인 곳에는 나도 그들 중에 있느니라</t>
+        </is>
+      </c>
       <c r="J23" s="7">
         <f>IF(I23="","",LEN(SUBSTITUTE(I23," ","")))</f>
         <v/>
@@ -1758,8 +2147,14 @@
         <f>IF(I23="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L23" s="10" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
+      <c r="L23" s="10" t="n"/>
+      <c r="M23" s="10" t="n"/>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>두 세 사람이 내 이름으로 모인 곳에는 나도 그들 중에 있느니라</t>
+        </is>
+      </c>
+      <c r="O23" s="15" t="inlineStr"/>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -1798,7 +2193,11 @@
           <t>히브리서 10장 24-25절</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>서로 돌아보아 사랑과 선행을 격려하며 모이기를 폐하는 어떤 사람들의 습관과 같이 하지 말고 오직 권하여 그 날이 가까움을 볼수록 더욱 그리하자</t>
+        </is>
+      </c>
       <c r="J24" s="7">
         <f>IF(I24="","",LEN(SUBSTITUTE(I24," ","")))</f>
         <v/>
@@ -1807,8 +2206,14 @@
         <f>IF(I24="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L24" s="10" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
+      <c r="L24" s="10" t="n"/>
+      <c r="M24" s="10" t="n"/>
+      <c r="N24" s="14" t="inlineStr">
+        <is>
+          <t>서로 돌아보아 사랑과 선행을 격려하며 모이기를 폐하는 어떤 사람들의 습관과 같이 하지 말고 오직 권하여 그날이 가까움을 볼수록 더욱 그리하자</t>
+        </is>
+      </c>
+      <c r="O24" s="15" t="inlineStr"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="7" t="n">
@@ -1847,7 +2252,11 @@
           <t>마태복음 4장 19절</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr"/>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>말씀하시되 나를 따라오라 내가 너희를 사람을 낚는 어부가 되게 하리라 하시니</t>
+        </is>
+      </c>
       <c r="J25" s="7">
         <f>IF(I25="","",LEN(SUBSTITUTE(I25," ","")))</f>
         <v/>
@@ -1856,8 +2265,18 @@
         <f>IF(I25="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L25" s="10" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
+      <c r="L25" s="10" t="n"/>
+      <c r="M25" s="10" t="n"/>
+      <c r="N25" s="14" t="inlineStr">
+        <is>
+          <t>말씀하시되 나를 따라 오너라 내가 너희로 사람을 낚는 어부가 되게 하리라 하시니</t>
+        </is>
+      </c>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -1896,7 +2315,11 @@
           <t>로마서 1장 16절</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr"/>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>내가 복음을 부끄러워하지 아니하노니 이 복음은 모든 믿는 자에게 구원을 주시는 하나님의 능력이 됨이라 먼저는 유대인에게요 그리고 헬라인에게로다</t>
+        </is>
+      </c>
       <c r="J26" s="7">
         <f>IF(I26="","",LEN(SUBSTITUTE(I26," ","")))</f>
         <v/>
@@ -1905,8 +2328,18 @@
         <f>IF(I26="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L26" s="10" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
+      <c r="L26" s="10" t="n"/>
+      <c r="M26" s="10" t="n"/>
+      <c r="N26" s="14" t="inlineStr">
+        <is>
+          <t>내가 복음을 부끄러워하지 아니하노니 이 복음은 모든 믿는 자에게 구원을 주시는 하나님의 능력이 됨이라 첫째는 유대인에게요 또한 헬라인에게로다</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="7" t="n">
@@ -1945,7 +2378,11 @@
           <t>로마서 3장 23절</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr"/>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>모든 사람이 죄를 범하였으매 하나님의 영광에 이르지 못하더니</t>
+        </is>
+      </c>
       <c r="J27" s="7">
         <f>IF(I27="","",LEN(SUBSTITUTE(I27," ","")))</f>
         <v/>
@@ -1954,8 +2391,14 @@
         <f>IF(I27="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L27" s="10" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
+      <c r="L27" s="10" t="n"/>
+      <c r="M27" s="10" t="n"/>
+      <c r="N27" s="14" t="inlineStr">
+        <is>
+          <t>모든 사람이 죄를 범하였으매 하나님의 영광에 이르지 못하더니</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="inlineStr"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="7" t="n">
@@ -1994,7 +2437,11 @@
           <t>이사야 53장 6절</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr"/>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>우리는 다 양 같아서 그릇 행하여 각기 제 길로 갔거늘 여호와께서는 우리 모두의 죄악을 그에게 담당시키셨도다</t>
+        </is>
+      </c>
       <c r="J28" s="7">
         <f>IF(I28="","",LEN(SUBSTITUTE(I28," ","")))</f>
         <v/>
@@ -2003,8 +2450,18 @@
         <f>IF(I28="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L28" s="10" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
+      <c r="L28" s="10" t="n"/>
+      <c r="M28" s="10" t="n"/>
+      <c r="N28" s="14" t="inlineStr">
+        <is>
+          <t>우리는 다 양 같아서 그릇 행하여 각기 제 길로 갔거늘 여호와께서는 우리 무리의 죄악을 그에게 담당시키셨도다</t>
+        </is>
+      </c>
+      <c r="O28" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="7" t="n">
@@ -2043,7 +2500,11 @@
           <t>로마서 6장 23절</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr"/>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>죄의 삯은 사망이요 하나님의 은사는 그리스도 예수 우리 주 안에 있는 영생이니라</t>
+        </is>
+      </c>
       <c r="J29" s="7">
         <f>IF(I29="","",LEN(SUBSTITUTE(I29," ","")))</f>
         <v/>
@@ -2052,8 +2513,14 @@
         <f>IF(I29="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L29" s="10" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
+      <c r="L29" s="10" t="n"/>
+      <c r="M29" s="10" t="n"/>
+      <c r="N29" s="14" t="inlineStr">
+        <is>
+          <t>죄의 삯은 사망이요 하나님의 은사는 그리스도 예수 우리 주 안에 있는 영생이니라</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="inlineStr"/>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="7" t="n">
@@ -2092,7 +2559,11 @@
           <t>히브리서 9장 27절</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr"/>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>한 번 죽는 것은 사람에게 정해진 것이요 그 후에는 심판이 있으리니</t>
+        </is>
+      </c>
       <c r="J30" s="7">
         <f>IF(I30="","",LEN(SUBSTITUTE(I30," ","")))</f>
         <v/>
@@ -2101,8 +2572,18 @@
         <f>IF(I30="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L30" s="10" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
+      <c r="L30" s="10" t="n"/>
+      <c r="M30" s="10" t="n"/>
+      <c r="N30" s="14" t="inlineStr">
+        <is>
+          <t>한번 죽는 것은 사람에게 정하신 것이요 그 후에는 심판이 있으리니</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="7" t="n">
@@ -2141,7 +2622,11 @@
           <t>로마서 5장 8절</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>우리가 아직 죄인 되었을 때에 그리스도께서 우리를 위하여 죽으심으로 하나님께서 우리에 대한 자기의 사랑을 확증하셨느니라</t>
+        </is>
+      </c>
       <c r="J31" s="7">
         <f>IF(I31="","",LEN(SUBSTITUTE(I31," ","")))</f>
         <v/>
@@ -2150,8 +2635,18 @@
         <f>IF(I31="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L31" s="10" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
+      <c r="L31" s="10" t="n"/>
+      <c r="M31" s="10" t="n"/>
+      <c r="N31" s="14" t="inlineStr">
+        <is>
+          <t>우리가 아직 죄인 되었을 때에 그리스도께서 우리를 위하여 죽으심으로 하나님께서 우리에게 대한 자기의 사랑을 확증하셨느니라</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="7" t="n">
@@ -2190,7 +2685,11 @@
           <t>베드로전서 3장 18절</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>그리스도께서도 단번에 죄를 위하여 죽으사 의인으로서 불의한 자를 대신하셨으니 이는 우리를 하나님 앞으로 인도하려 하심이라 육체로는 죽임을 당하시고 영으로는 살리심을 받으셨으니</t>
+        </is>
+      </c>
       <c r="J32" s="7">
         <f>IF(I32="","",LEN(SUBSTITUTE(I32," ","")))</f>
         <v/>
@@ -2199,8 +2698,18 @@
         <f>IF(I32="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L32" s="10" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
+      <c r="L32" s="10" t="n"/>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="14" t="inlineStr">
+        <is>
+          <t>그리스도께서도 한번 죄를 위하여 죽으사 의인으로서 불의한 자를 대신하셨으니 이는 우리를 하나님 앞으로 인도하려 하심이라 육체로는 죽임을 당하시고 영으로는 살리심을 받으셨으니</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="7" t="n">
@@ -2239,7 +2748,11 @@
           <t>에베소서 2장 8-9절</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>너희는 그 은혜에 의하여 믿음으로 말미암아 구원을 받았으니 이것은 너희에게서 난 것이 아니요 하나님의 선물이라 행위에서 난 것이 아니니 이는 누구든지 자랑하지 못하게 함이라</t>
+        </is>
+      </c>
       <c r="J33" s="7">
         <f>IF(I33="","",LEN(SUBSTITUTE(I33," ","")))</f>
         <v/>
@@ -2248,8 +2761,18 @@
         <f>IF(I33="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L33" s="10" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
+      <c r="L33" s="10" t="n"/>
+      <c r="M33" s="10" t="n"/>
+      <c r="N33" s="14" t="inlineStr">
+        <is>
+          <t>너희가 그 은혜를 인하여 믿음으로 말미암아 구원을 얻었나니 이것이 너희에게서 난 것이 아니요 하나님의 선물이라 행위에서 난 것이 아니니 이는 누구든지 자랑치 못하게 함이니라</t>
+        </is>
+      </c>
+      <c r="O33" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="7" t="n">
@@ -2288,7 +2811,11 @@
           <t>디도서 3장 5절</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>우리를 구원하시되 우리가 행한 바 의로운 행위로 말미암지 아니하고 오직 그의 긍휼하심을 따라 중생의 씻음과 성령의 새롭게 하심으로 하셨나니</t>
+        </is>
+      </c>
       <c r="J34" s="7">
         <f>IF(I34="","",LEN(SUBSTITUTE(I34," ","")))</f>
         <v/>
@@ -2297,8 +2824,18 @@
         <f>IF(I34="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L34" s="10" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
+      <c r="L34" s="10" t="n"/>
+      <c r="M34" s="10" t="n"/>
+      <c r="N34" s="14" t="inlineStr">
+        <is>
+          <t>우리를 구원하시되 우리의 행한바 의로운 행위로 말미암지 아니하고 오직 그의 긍휼하심을 좇아 중생의 씻음과 성령의 새롭게 하심으로 하셨나니</t>
+        </is>
+      </c>
+      <c r="O34" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="7" t="n">
@@ -2337,7 +2874,11 @@
           <t>요한복음 1장 12절</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr"/>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>영접하는 자 곧 그 이름을 믿는 자들에게는 하나님의 자녀가 되는 권세를 주셨으니</t>
+        </is>
+      </c>
       <c r="J35" s="7">
         <f>IF(I35="","",LEN(SUBSTITUTE(I35," ","")))</f>
         <v/>
@@ -2346,8 +2887,14 @@
         <f>IF(I35="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L35" s="10" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
+      <c r="L35" s="10" t="n"/>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="14" t="inlineStr">
+        <is>
+          <t>영접하는 자 곧 그 이름을 믿는 자들에게는 하나님의 자녀가 되는 권세를 주셨으니</t>
+        </is>
+      </c>
+      <c r="O35" s="15" t="inlineStr"/>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="7" t="n">
@@ -2386,7 +2933,11 @@
           <t>요한계시록 3장 20절</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr"/>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>볼지어다 내가 문 밖에 서서 두드리노니 누구든지 내 음성을 듣고 문을 열면 내가 그에게로 들어가 그와 더불어 먹고 그는 나와 더불어 먹으리라</t>
+        </is>
+      </c>
       <c r="J36" s="7">
         <f>IF(I36="","",LEN(SUBSTITUTE(I36," ","")))</f>
         <v/>
@@ -2395,8 +2946,18 @@
         <f>IF(I36="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L36" s="10" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
+      <c r="L36" s="10" t="n"/>
+      <c r="M36" s="10" t="n"/>
+      <c r="N36" s="14" t="inlineStr">
+        <is>
+          <t>볼지어다 내가 문밖에 서서 두드리노니 누구든지 내 음성을 듣고 문을 열면 내가 그에게로 들어가 그로 더불어 먹고 그는 나로 더불어 먹으리라</t>
+        </is>
+      </c>
+      <c r="O36" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="7" t="n">
@@ -2435,7 +2996,11 @@
           <t>요한일서 5장 13절</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr"/>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>내가 하나님의 아들의 이름을 믿는 너희에게 이것을 쓰는 것은 너희로 하여금 너희에게 영생이 있음을 알게 하려 함이라</t>
+        </is>
+      </c>
       <c r="J37" s="7">
         <f>IF(I37="","",LEN(SUBSTITUTE(I37," ","")))</f>
         <v/>
@@ -2444,8 +3009,18 @@
         <f>IF(I37="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L37" s="10" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
+      <c r="L37" s="10" t="n"/>
+      <c r="M37" s="10" t="n"/>
+      <c r="N37" s="14" t="inlineStr">
+        <is>
+          <t>내가 하나님의 아들의 이름을 믿는 너희에게 이것을 쓴 것은 너희로 하여금 너희에게 영생이 있음을 알게 하려 함이라</t>
+        </is>
+      </c>
+      <c r="O37" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="7" t="n">
@@ -2484,7 +3059,11 @@
           <t>요한복음 5장 24절</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr"/>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>내가 진실로 진실로 너희에게 이르노니 내 말을 듣고 또 나 보내신 이를 믿는 자는 영생을 얻었고 심판에 이르지 아니하나니 사망에서 생명으로 옮겼느니라</t>
+        </is>
+      </c>
       <c r="J38" s="7">
         <f>IF(I38="","",LEN(SUBSTITUTE(I38," ","")))</f>
         <v/>
@@ -2493,8 +3072,14 @@
         <f>IF(I38="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L38" s="10" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="14" t="inlineStr">
+        <is>
+          <t>내가 진실로 진실로 너희에게 이르노니 내 말을 듣고 또 나 보내신 이를 믿는 자는 영생을 얻었고 심판에 이르지 아니하나니 사망에서 생명으로 옮겼느니라</t>
+        </is>
+      </c>
+      <c r="O38" s="15" t="inlineStr"/>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="7" t="n">
@@ -2533,7 +3118,11 @@
           <t>고린도전서 3장 16절</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr"/>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>너희는 너희가 하나님의 성전인 것과 하나님의 성령이 너희 안에 계시는 것을 알지 못하느냐</t>
+        </is>
+      </c>
       <c r="J39" s="7">
         <f>IF(I39="","",LEN(SUBSTITUTE(I39," ","")))</f>
         <v/>
@@ -2542,8 +3131,18 @@
         <f>IF(I39="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L39" s="10" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
+      <c r="L39" s="10" t="n"/>
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="14" t="inlineStr">
+        <is>
+          <t>너희가 하나님의 성전인 것과 하나님의 성령이 너희 안에 거하시는 것을 알지 못하느뇨</t>
+        </is>
+      </c>
+      <c r="O39" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="7" t="n">
@@ -2582,7 +3181,11 @@
           <t>고린도전서 2장 12절</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr"/>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>우리가 세상의 영을 받지 아니하고 오직 하나님으로부터 온 영을 받았으니 이는 우리로 하여금 하나님께서 우리에게 은혜로 주신 것들을 알게 하려 하심이라</t>
+        </is>
+      </c>
       <c r="J40" s="7">
         <f>IF(I40="","",LEN(SUBSTITUTE(I40," ","")))</f>
         <v/>
@@ -2591,8 +3194,18 @@
         <f>IF(I40="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L40" s="10" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
+      <c r="L40" s="10" t="n"/>
+      <c r="M40" s="10" t="n"/>
+      <c r="N40" s="14" t="inlineStr">
+        <is>
+          <t>우리가 세상의 영을 받지 아니하고 오직 하나님께로 온 영을 받았으니 이는 우리로 하여금 하나님께서 우리에게 은혜로 주신 것들을 알게 하려 하심이라</t>
+        </is>
+      </c>
+      <c r="O40" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="7" t="n">
@@ -2631,7 +3244,11 @@
           <t>이사야 41장 10절</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr"/>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>두려워하지 말라 내가 너와 함께 함이라 놀라지 말라 나는 네 하나님이 됨이라 내가 너를 굳세게 하리라 참으로 너를 도와 주리라 참으로 나의 의로운 오른손으로 너를 붙들리라</t>
+        </is>
+      </c>
       <c r="J41" s="7">
         <f>IF(I41="","",LEN(SUBSTITUTE(I41," ","")))</f>
         <v/>
@@ -2640,8 +3257,18 @@
         <f>IF(I41="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L41" s="10" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="14" t="inlineStr">
+        <is>
+          <t>두려워 말라 내가 너와 함께 함이니라 놀라지 말라 나는 네 하나님이 됨이니라 내가 너를 굳세게 하리라 참으로 너를 도와 주리라 참으로 나의 의로운 오른손으로 너를 붙들리라</t>
+        </is>
+      </c>
+      <c r="O41" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="7" t="n">
@@ -2680,7 +3307,11 @@
           <t>빌립보서 4장 13절</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>내게 능력 주시는 자 안에서 내가 모든 것을 할 수 있느니라</t>
+        </is>
+      </c>
       <c r="J42" s="7">
         <f>IF(I42="","",LEN(SUBSTITUTE(I42," ","")))</f>
         <v/>
@@ -2689,8 +3320,14 @@
         <f>IF(I42="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L42" s="10" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="14" t="inlineStr">
+        <is>
+          <t>내게 능력 주시는 자 안에서 내가 모든 것을 할 수 있느니라</t>
+        </is>
+      </c>
+      <c r="O42" s="15" t="inlineStr"/>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="7" t="n">
@@ -2729,7 +3366,11 @@
           <t>예레미야애가 3장 22-23절</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr"/>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>여호와의 인자와 긍휼이 무궁하시므로 우리가 진멸되지 아니함이니이다 이것들이 아침마다 새로우니 주의 성실하심이 크시도소이다</t>
+        </is>
+      </c>
       <c r="J43" s="7">
         <f>IF(I43="","",LEN(SUBSTITUTE(I43," ","")))</f>
         <v/>
@@ -2738,8 +3379,18 @@
         <f>IF(I43="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L43" s="10" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
+      <c r="L43" s="10" t="n"/>
+      <c r="M43" s="10" t="n"/>
+      <c r="N43" s="14" t="inlineStr">
+        <is>
+          <t>여호와의 자비와 긍휼이 무궁하시므로 우리가 진멸되지 아니함이니이다 이것이 아침마다 새로우니 주의 성실이 크도소이다</t>
+        </is>
+      </c>
+      <c r="O43" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="7" t="n">
@@ -2778,7 +3429,11 @@
           <t>민수기 23장 19절</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr"/>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>하나님은 사람이 아니시니 거짓말을 하지 않으시고 인생이 아니시니 후회가 없으시도다 어찌 그 말씀하신 바를 행하지 않으시며 하신 말씀을 실행하지 않으시랴</t>
+        </is>
+      </c>
       <c r="J44" s="7">
         <f>IF(I44="","",LEN(SUBSTITUTE(I44," ","")))</f>
         <v/>
@@ -2787,8 +3442,18 @@
         <f>IF(I44="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L44" s="10" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
+      <c r="L44" s="10" t="n"/>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="14" t="inlineStr">
+        <is>
+          <t>하나님은 인생이 아니시니 식언치 않으시고 인자가 아니시니 후회가 없으시도다 어찌 그 말씀하신 바를 행치 않으시며 하신 말씀을 실행치 않으시랴</t>
+        </is>
+      </c>
+      <c r="O44" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="7" t="n">
@@ -2827,7 +3492,11 @@
           <t>이사야 26장 3절</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr"/>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>주께서 심지가 견고한 자를 평강하고 평강하도록 지키시리니 이는 그가 주를 신뢰함이니이다</t>
+        </is>
+      </c>
       <c r="J45" s="7">
         <f>IF(I45="","",LEN(SUBSTITUTE(I45," ","")))</f>
         <v/>
@@ -2836,8 +3505,18 @@
         <f>IF(I45="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L45" s="10" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="n"/>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="14" t="inlineStr">
+        <is>
+          <t>주께서 심지가 견고한 자를 평강에 평강으로 지키시리니 이는 그가 주를 의뢰함이니이다</t>
+        </is>
+      </c>
+      <c r="O45" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="7" t="n">
@@ -2876,7 +3555,11 @@
           <t>베드로전서 5장 7절</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr"/>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>너희 염려를 다 주께 맡기라 이는 그가 너희를 돌보심이라</t>
+        </is>
+      </c>
       <c r="J46" s="7">
         <f>IF(I46="","",LEN(SUBSTITUTE(I46," ","")))</f>
         <v/>
@@ -2885,8 +3568,18 @@
         <f>IF(I46="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L46" s="10" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
+      <c r="L46" s="10" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="14" t="inlineStr">
+        <is>
+          <t>너희 염려를 다 주께 맡겨 버리라 이는 저가 너희를 권고하심이니라</t>
+        </is>
+      </c>
+      <c r="O46" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="7" t="n">
@@ -2925,7 +3618,11 @@
           <t>로마서 8장 32절</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr"/>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>자기 아들을 아끼지 아니하시고 우리 모든 사람을 위하여 내주신 이가 어찌 그 아들과 함께 모든 것을 우리에게 주시지 아니하겠느냐</t>
+        </is>
+      </c>
       <c r="J47" s="7">
         <f>IF(I47="","",LEN(SUBSTITUTE(I47," ","")))</f>
         <v/>
@@ -2934,8 +3631,18 @@
         <f>IF(I47="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L47" s="10" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
+      <c r="L47" s="10" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="14" t="inlineStr">
+        <is>
+          <t>자기 아들을 아끼지 아니하시고 우리 모든 사람을 위하여 내어 주신 이가 어찌 그 아들과 함께 모든 것을 우리에게 은사로 주지 아니 하시겠느뇨</t>
+        </is>
+      </c>
+      <c r="O47" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="7" t="n">
@@ -2974,7 +3681,11 @@
           <t>빌립보서 4장 19절</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr"/>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>나의 하나님이 그리스도 예수 안에서 영광 가운데 그 풍성한 대로 너희 모든 쓸 것을 채우시리라</t>
+        </is>
+      </c>
       <c r="J48" s="7">
         <f>IF(I48="","",LEN(SUBSTITUTE(I48," ","")))</f>
         <v/>
@@ -2983,8 +3694,14 @@
         <f>IF(I48="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L48" s="10" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
+      <c r="L48" s="10" t="n"/>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="14" t="inlineStr">
+        <is>
+          <t>나의 하나님이 그리스도 예수 안에서 영광 가운데 그 풍성한 대로 너희 모든 쓸 것을 채우시리라</t>
+        </is>
+      </c>
+      <c r="O48" s="15" t="inlineStr"/>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="7" t="n">
@@ -3023,7 +3740,11 @@
           <t>히브리서 2장 18절</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr"/>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>그가 시험을 받아 고난을 당하셨은즉 시험 받는 자들을 능히 도우실 수 있느니라</t>
+        </is>
+      </c>
       <c r="J49" s="7">
         <f>IF(I49="","",LEN(SUBSTITUTE(I49," ","")))</f>
         <v/>
@@ -3032,8 +3753,18 @@
         <f>IF(I49="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L49" s="10" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
+      <c r="L49" s="10" t="n"/>
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="14" t="inlineStr">
+        <is>
+          <t>자기가 시험을 받아 고난을 당하셨은즉 시험받는 자들을 능히 도우시느니라</t>
+        </is>
+      </c>
+      <c r="O49" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="7" t="n">
@@ -3072,7 +3803,11 @@
           <t>시편 119편 9, 11절</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr"/>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>청년이 무엇으로 그의 행실을 깨끗하게 하리이까 주의 말씀만 지킬 따름이니이다 내가 주께 범죄하지 아니하려 하여 주의 말씀을 내 마음에 두었나이다</t>
+        </is>
+      </c>
       <c r="J50" s="7">
         <f>IF(I50="","",LEN(SUBSTITUTE(I50," ","")))</f>
         <v/>
@@ -3081,8 +3816,18 @@
         <f>IF(I50="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L50" s="10" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
+      <c r="L50" s="10" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="14" t="inlineStr">
+        <is>
+          <t>청년이 무엇으로 그 행실을 깨끗케 하리이까 주의 말씀을 따라 삼갈 것이니이다 내가 주께 범죄치 아니하려 하여 주의 말씀을 내 마음에 두었나이다</t>
+        </is>
+      </c>
+      <c r="O50" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="7" t="n">
@@ -3121,7 +3866,11 @@
           <t>마태복음 6장 33절</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr"/>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>그런즉 너희는 먼저 그의 나라와 그의 의를 구하라 그리하면 이 모든 것을 너희에게 더하시리라</t>
+        </is>
+      </c>
       <c r="J51" s="7">
         <f>IF(I51="","",LEN(SUBSTITUTE(I51," ","")))</f>
         <v/>
@@ -3130,8 +3879,18 @@
         <f>IF(I51="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L51" s="10" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
+      <c r="L51" s="10" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="14" t="inlineStr">
+        <is>
+          <t>너희는 먼저 그의 나라와 그의 의를 구하라 그리하면 이 모든 것을 너희에게 더하시리라</t>
+        </is>
+      </c>
+      <c r="O51" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="7" t="n">
@@ -3170,7 +3929,11 @@
           <t>누가복음 9장 23절</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr"/>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>또 무리에게 이르시되 아무든지 나를 따라오려거든 자기를 부인하고 날마다 제 십자가를 지고 나를 따를 것이니라</t>
+        </is>
+      </c>
       <c r="J52" s="7">
         <f>IF(I52="","",LEN(SUBSTITUTE(I52," ","")))</f>
         <v/>
@@ -3179,8 +3942,18 @@
         <f>IF(I52="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L52" s="10" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
+      <c r="L52" s="10" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="14" t="inlineStr">
+        <is>
+          <t>또 무리에게 이르시되 아무든지 나를 따라 오려거든 자기를 부인하고 날마다 제 십자가를 지고 나를 좇을 것이니라</t>
+        </is>
+      </c>
+      <c r="O52" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="7" t="n">
@@ -3219,7 +3992,11 @@
           <t>요한일서 2장 15-16절</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr"/>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>이 세상이나 세상에 있는 것들을 사랑하지 말라 누구든지 세상을 사랑하면 아버지의 사랑이 그 안에 있지 아니하니 이는 세상에 있는 모든 것이 육신의 정욕과 안목의 정욕과 이생의 자랑이니 다 아버지께로부터 온 것이 아니요 세상으로부터 온 것이라</t>
+        </is>
+      </c>
       <c r="J53" s="7">
         <f>IF(I53="","",LEN(SUBSTITUTE(I53," ","")))</f>
         <v/>
@@ -3228,8 +4005,18 @@
         <f>IF(I53="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L53" s="10" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
+      <c r="L53" s="10" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="14" t="inlineStr">
+        <is>
+          <t>이 세상이나 세상에 있는 것들을 사랑치 말라 누구든지 세상을 사랑하면 아버지의 사랑이 그 속에 있지 아니하니 이는 세상에 있는 모든 것이 육신의 정욕과 안목의 정욕과 이생의 자랑이니 다 아버지께로 좇아 온 것이 아니요 세상으로 좇아 온 것이라</t>
+        </is>
+      </c>
+      <c r="O53" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="7" t="n">
@@ -3268,7 +4055,11 @@
           <t>로마서 12장 2절</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr"/>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>너희는 이 세대를 본받지 말고 오직 마음을 새롭게 함으로 변화를 받아 하나님의 선하시고 기뻐하시고 온전하신 뜻이 무엇인지 분별하도록 하라</t>
+        </is>
+      </c>
       <c r="J54" s="7">
         <f>IF(I54="","",LEN(SUBSTITUTE(I54," ","")))</f>
         <v/>
@@ -3277,8 +4068,14 @@
         <f>IF(I54="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L54" s="10" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="14" t="inlineStr">
+        <is>
+          <t>너희는 이 세대를 본받지 말고 오직 마음을 새롭게 함으로 변화를 받아 하나님의 선하시고 기뻐하시고 온전하신 뜻이 무엇인지 분별하도록 하라</t>
+        </is>
+      </c>
+      <c r="O54" s="15" t="inlineStr"/>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="7" t="n">
@@ -3317,7 +4114,11 @@
           <t>고린도전서 15장 58절</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr"/>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>그러므로 내 사랑하는 형제들아 견실하며 흔들리지 말고 항상 주의 일에 더욱 힘쓰는 자들이 되라 이는 너희 수고가 주 안에서 헛되지 않은 줄 앎이라</t>
+        </is>
+      </c>
       <c r="J55" s="7">
         <f>IF(I55="","",LEN(SUBSTITUTE(I55," ","")))</f>
         <v/>
@@ -3326,8 +4127,18 @@
         <f>IF(I55="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L55" s="10" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="14" t="inlineStr">
+        <is>
+          <t>그러므로 내 사랑하는 형제들아 견고하며 흔들리지 말며 항상 주의 일에 더욱 힘쓰는 자들이 되라 이는 너희 수고가 주 안에서 헛되지 않은 줄을 앎이니라</t>
+        </is>
+      </c>
+      <c r="O55" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="7" t="n">
@@ -3366,7 +4177,11 @@
           <t>히브리서 12장 3절</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr"/>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>너희가 피곤하여 낙심하지 않기 위하여 죄인들이 이같이 자기에게 거역한 일을 참으신 이를 생각하라</t>
+        </is>
+      </c>
       <c r="J56" s="7">
         <f>IF(I56="","",LEN(SUBSTITUTE(I56," ","")))</f>
         <v/>
@@ -3375,8 +4190,18 @@
         <f>IF(I56="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L56" s="10" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
+      <c r="L56" s="10" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="14" t="inlineStr">
+        <is>
+          <t>너희가 피곤하여 낙심치 않기 위하여 죄인들의 이같이 자기에게 거역한 일을 참으신 자를 생각하라</t>
+        </is>
+      </c>
+      <c r="O56" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="7" t="n">
@@ -3415,7 +4240,11 @@
           <t>마가복음 10장 45절</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr"/>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>인자가 온 것은 섬김을 받으려 함이 아니라 도리어 섬기려 하고 자기 목숨을 많은 사람의 대속물로 주려 함이니라</t>
+        </is>
+      </c>
       <c r="J57" s="7">
         <f>IF(I57="","",LEN(SUBSTITUTE(I57," ","")))</f>
         <v/>
@@ -3424,8 +4253,18 @@
         <f>IF(I57="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L57" s="10" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="14" t="inlineStr">
+        <is>
+          <t>인자의 온 것은 섬김을 받으려 함이 아니라 도리어 섬기려 하고 자기 목숨을 많은 사람의 대속물로 주려 함이니라</t>
+        </is>
+      </c>
+      <c r="O57" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="7" t="n">
@@ -3464,7 +4303,11 @@
           <t>고린도후서 4장 5절</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr"/>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>우리는 우리를 전파하는 것이 아니라 오직 그리스도 예수의 주 되신 것과 또 예수를 위하여 우리가 너희의 종 된 것을 전파함이라</t>
+        </is>
+      </c>
       <c r="J58" s="7">
         <f>IF(I58="","",LEN(SUBSTITUTE(I58," ","")))</f>
         <v/>
@@ -3473,8 +4316,18 @@
         <f>IF(I58="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L58" s="10" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="14" t="inlineStr">
+        <is>
+          <t>우리가 우리를 전파하는 것이 아니라 오직 그리스도 예수의 주 되신 것과 또 예수를 위하여 우리가 너희의 종 된 것을 전파함이라</t>
+        </is>
+      </c>
+      <c r="O58" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="7" t="n">
@@ -3513,7 +4366,11 @@
           <t>잠언 3장 9-10절</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr"/>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>네 재물과 네 소산물의 처음 익은 열매로 여호와를 공경하라 그리하면 네 창고가 가득히 차고 네 포도즙 틀에 새 포도즙이 넘치리라</t>
+        </is>
+      </c>
       <c r="J59" s="7">
         <f>IF(I59="","",LEN(SUBSTITUTE(I59," ","")))</f>
         <v/>
@@ -3522,8 +4379,18 @@
         <f>IF(I59="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L59" s="10" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="14" t="inlineStr">
+        <is>
+          <t>네 재물과 네 소산물의 처음 익은 열매로 여호와를 공경하라 그리하면 네 창고가 가득히 차고 네 즙틀에 새 포도즙이 넘치리라</t>
+        </is>
+      </c>
+      <c r="O59" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="7" t="n">
@@ -3562,7 +4429,11 @@
           <t>고린도후서 9장 6-7절</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr"/>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>이것이 곧 적게 심는 자는 적게 거두고 많이 심는 자는 많이 거둔다 하는 말이로다 각각 그 마음에 정한 대로 할 것이요 인색함으로나 억지로 하지 말지니 하나님은 즐겨 내는 자를 사랑하시느니라</t>
+        </is>
+      </c>
       <c r="J60" s="7">
         <f>IF(I60="","",LEN(SUBSTITUTE(I60," ","")))</f>
         <v/>
@@ -3571,8 +4442,14 @@
         <f>IF(I60="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L60" s="10" t="inlineStr"/>
-      <c r="M60" s="10" t="inlineStr"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="14" t="inlineStr">
+        <is>
+          <t>이것이 곧 적게 심는 자는 적게 거두고 많이 심는 자는 많이 거둔다 하는 말이로다 각각 그 마음에 정한대로 할 것이요 인색함으로나 억지로 하지 말지니 하나님은 즐겨 내는 자를 사랑하시느니라</t>
+        </is>
+      </c>
+      <c r="O60" s="15" t="inlineStr"/>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="7" t="n">
@@ -3611,7 +4488,11 @@
           <t>사도행전 1장 8절</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr"/>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>오직 성령이 너희에게 임하시면 너희가 권능을 받고 예루살렘과 온 유대와 사마리아와 땅 끝까지 이르러 내 증인이 되리라 하시니라</t>
+        </is>
+      </c>
       <c r="J61" s="7">
         <f>IF(I61="","",LEN(SUBSTITUTE(I61," ","")))</f>
         <v/>
@@ -3620,8 +4501,14 @@
         <f>IF(I61="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L61" s="10" t="inlineStr"/>
-      <c r="M61" s="10" t="inlineStr"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="14" t="inlineStr">
+        <is>
+          <t>오직 성령이 너희에게 임하시면 너희가 권능을 받고 예루살렘과 온 유대와 사마리아와 땅끝까지 이르러 내 증인이 되리라 하시니라</t>
+        </is>
+      </c>
+      <c r="O61" s="15" t="inlineStr"/>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="7" t="n">
@@ -3660,7 +4547,11 @@
           <t>마태복음 28장 19-20절</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr"/>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>그러므로 너희는 가서 모든 민족을 제자로 삼아 아버지와 아들과 성령의 이름으로 세례를 베풀고 내가 너희에게 분부한 모든 것을 가르쳐 지키게 하라 볼지어다 내가 세상 끝날까지 너희와 항상 함께 있으리라 하시니라</t>
+        </is>
+      </c>
       <c r="J62" s="7">
         <f>IF(I62="","",LEN(SUBSTITUTE(I62," ","")))</f>
         <v/>
@@ -3669,8 +4560,18 @@
         <f>IF(I62="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L62" s="10" t="inlineStr"/>
-      <c r="M62" s="10" t="inlineStr"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="14" t="inlineStr">
+        <is>
+          <t>그러므로 너희는 가서 모든 족속으로 제자를 삼아 아버지와 아들과 성령의 이름으로 세례를 주고 내가 너희에게 분부한 모든 것을 가르쳐 지키게 하라 볼지어다 내가 세상 끝날까지 너희와 항상 함께 있으리라 하시니라</t>
+        </is>
+      </c>
+      <c r="O62" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="7" t="n">
@@ -3709,7 +4610,11 @@
           <t>요한복음 13장 34-35절</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr"/>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>새 계명을 너희에게 주노니 서로 사랑하라 내가 너희를 사랑한 것 같이 너희도 서로 사랑하라 너희가 서로 사랑하면 이로써 모든 사람이 너희가 내 제자인 줄 알리라</t>
+        </is>
+      </c>
       <c r="J63" s="7">
         <f>IF(I63="","",LEN(SUBSTITUTE(I63," ","")))</f>
         <v/>
@@ -3718,8 +4623,14 @@
         <f>IF(I63="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L63" s="10" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="14" t="inlineStr">
+        <is>
+          <t>새 계명을 너희에게 주노니 서로 사랑하라 내가 너희를 사랑한 것 같이 너희도 서로 사랑하라 너희가 서로 사랑하면 이로써 모든 사람이 너희가 내 제자인 줄 알리라</t>
+        </is>
+      </c>
+      <c r="O63" s="15" t="inlineStr"/>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="7" t="n">
@@ -3758,7 +4669,11 @@
           <t>요한일서 3장 18절</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr"/>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>자녀들아 우리가 말과 혀로만 사랑하지 말고 행함과 진실함으로 하자</t>
+        </is>
+      </c>
       <c r="J64" s="7">
         <f>IF(I64="","",LEN(SUBSTITUTE(I64," ","")))</f>
         <v/>
@@ -3767,8 +4682,18 @@
         <f>IF(I64="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L64" s="10" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="14" t="inlineStr">
+        <is>
+          <t>자녀들아 우리가 말과 혀로만 사랑하지 말고 오직 행함과 진실함으로 하자</t>
+        </is>
+      </c>
+      <c r="O64" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="7" t="n">
@@ -3807,7 +4732,11 @@
           <t>빌립보서 2장 3-4절</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr"/>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>아무 일에든지 다툼이나 허영으로 하지 말고 오직 겸손한 마음으로 각각 자기보다 남을 낫게 여기고 각각 자기 일을 돌볼뿐더러 또한 각각 다른 사람들의 일을 돌보아 나의 기쁨을 충만하게 하라</t>
+        </is>
+      </c>
       <c r="J65" s="7">
         <f>IF(I65="","",LEN(SUBSTITUTE(I65," ","")))</f>
         <v/>
@@ -3816,8 +4745,18 @@
         <f>IF(I65="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L65" s="10" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="14" t="inlineStr">
+        <is>
+          <t>아무 일에든지 다툼이나 허영으로 하지 말고 오직 겸손한 마음으로 각각 자기보다 남을 낫게 여기고 각각 자기 일을 돌아볼 뿐더러 또한 각각 다른 사람들의 일을 돌아보아 나의 기쁨을 충만케 하라</t>
+        </is>
+      </c>
+      <c r="O65" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="7" t="n">
@@ -3856,7 +4795,11 @@
           <t>베드로전서 5장 5-6절</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr"/>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>젊은 자들아 이와 같이 장로들에게 순종하고 다 서로 겸손으로 허리를 동이라 하나님은 교만한 자를 대적하시되 겸손한 자들에게는 은혜를 주시느니라 그러므로 하나님의 능하신 손 아래에서 겸손하라 때가 되면 너희를 높이시리라</t>
+        </is>
+      </c>
       <c r="J66" s="7">
         <f>IF(I66="","",LEN(SUBSTITUTE(I66," ","")))</f>
         <v/>
@@ -3865,8 +4808,18 @@
         <f>IF(I66="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L66" s="10" t="inlineStr"/>
-      <c r="M66" s="10" t="inlineStr"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="14" t="inlineStr">
+        <is>
+          <t>젊은 자들아 이와 같이 장로들에게 순복하고 다 서로 겸손으로 허리를 동이라 하나님이 교만한 자를 대적하시되 겸손한 자들에게는 은혜를 주시느니라 그러므로 하나님의 능하신 손 아래서 겸손하라 때가 되면 너희를 높이시리라</t>
+        </is>
+      </c>
+      <c r="O66" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="7" t="n">
@@ -3905,7 +4858,11 @@
           <t>에베소서 5장 3절</t>
         </is>
       </c>
-      <c r="I67" s="10" t="inlineStr"/>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>음행과 온갖 더러운 것과 탐욕은 너희 중에서 그 이름조차도 부르지 말라 이는 성도에게 마땅한 바니라</t>
+        </is>
+      </c>
       <c r="J67" s="7">
         <f>IF(I67="","",LEN(SUBSTITUTE(I67," ","")))</f>
         <v/>
@@ -3914,8 +4871,18 @@
         <f>IF(I67="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L67" s="10" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="14" t="inlineStr">
+        <is>
+          <t>음행과 온갖 더러운 것과 탐욕은 너희 중에서 그 이름이라도 부르지 말라 이는 성도의 마땅한 바니라</t>
+        </is>
+      </c>
+      <c r="O67" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="7" t="n">
@@ -3954,7 +4921,11 @@
           <t>베드로전서 2장 11절</t>
         </is>
       </c>
-      <c r="I68" s="10" t="inlineStr"/>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>사랑하는 자들아 거류민과 나그네 같은 너희를 권하노니 영혼을 거슬러 싸우는 육체의 정욕을 제어하라</t>
+        </is>
+      </c>
       <c r="J68" s="7">
         <f>IF(I68="","",LEN(SUBSTITUTE(I68," ","")))</f>
         <v/>
@@ -3963,8 +4934,18 @@
         <f>IF(I68="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L68" s="10" t="inlineStr"/>
-      <c r="M68" s="10" t="inlineStr"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="14" t="inlineStr">
+        <is>
+          <t>사랑하는 자들아 나그네와 행인 같은 너희를 권하노니 영혼을 거스려 싸우는 육체의 정욕을 제어하라</t>
+        </is>
+      </c>
+      <c r="O68" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="7" t="n">
@@ -4003,7 +4984,11 @@
           <t>레위기 19장 11절</t>
         </is>
       </c>
-      <c r="I69" s="10" t="inlineStr"/>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>너희는 도둑질하지 말며 속이지 말며 서로 거짓말하지 말며</t>
+        </is>
+      </c>
       <c r="J69" s="7">
         <f>IF(I69="","",LEN(SUBSTITUTE(I69," ","")))</f>
         <v/>
@@ -4012,8 +4997,18 @@
         <f>IF(I69="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L69" s="10" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="14" t="inlineStr">
+        <is>
+          <t>너희는 도적질하지 말며 속이지 말며 서로 거짓말하지 말며</t>
+        </is>
+      </c>
+      <c r="O69" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="7" t="n">
@@ -4052,7 +5047,11 @@
           <t>사도행전 24장 16절</t>
         </is>
       </c>
-      <c r="I70" s="10" t="inlineStr"/>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>이것으로 말미암아 나도 하나님과 사람에 대하여 항상 양심에 거리낌이 없기를 힘쓰나이다</t>
+        </is>
+      </c>
       <c r="J70" s="7">
         <f>IF(I70="","",LEN(SUBSTITUTE(I70," ","")))</f>
         <v/>
@@ -4061,8 +5060,18 @@
         <f>IF(I70="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L70" s="10" t="inlineStr"/>
-      <c r="M70" s="10" t="inlineStr"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="14" t="inlineStr">
+        <is>
+          <t>이것을 인하여 나도 하나님과 사람을 대하여 항상 양심에 거리낌이 없기를 힘쓰노라</t>
+        </is>
+      </c>
+      <c r="O70" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="7" t="n">
@@ -4101,7 +5110,11 @@
           <t>히브리서 11장 6절</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr"/>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>믿음이 없이는 하나님을 기쁘시게 하지 못하나니 하나님께 나아가는 자는 반드시 그가 계신 것과 또한 그가 자기를 찾는 자들에게 상 주시는 이심을 믿어야 할지니라</t>
+        </is>
+      </c>
       <c r="J71" s="7">
         <f>IF(I71="","",LEN(SUBSTITUTE(I71," ","")))</f>
         <v/>
@@ -4110,8 +5123,18 @@
         <f>IF(I71="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L71" s="10" t="inlineStr"/>
-      <c r="M71" s="10" t="inlineStr"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="14" t="inlineStr">
+        <is>
+          <t>믿음이 없이는 기쁘시게 못하나니 하나님께 나아가는 자는 반드시 그가 계신 것과 또한 그가 자기를 찾는 자들에게 상 주시는 이심을 믿어야 할지니라</t>
+        </is>
+      </c>
+      <c r="O71" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="7" t="n">
@@ -4150,7 +5173,11 @@
           <t>로마서 4장 20-21절</t>
         </is>
       </c>
-      <c r="I72" s="10" t="inlineStr"/>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>믿음이 없어 하나님의 약속을 의심하지 않고 믿음으로 견고하여져서 하나님께 영광을 돌리며 약속하신 그것을 또한 능히 이루실 줄을 확신하였으니</t>
+        </is>
+      </c>
       <c r="J72" s="7">
         <f>IF(I72="","",LEN(SUBSTITUTE(I72," ","")))</f>
         <v/>
@@ -4159,8 +5186,18 @@
         <f>IF(I72="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L72" s="10" t="inlineStr"/>
-      <c r="M72" s="10" t="inlineStr"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="14" t="inlineStr">
+        <is>
+          <t>믿음이 없어 하나님의 약속을 의심치 않고 믿음에 견고하여져서 하나님께 영광을 돌리며 약속하신 그것을 또한 능히 이루실 줄을 확신하였으니</t>
+        </is>
+      </c>
+      <c r="O72" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="7" t="n">
@@ -4199,7 +5236,11 @@
           <t>갈라디아서 6장 9-10절</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr"/>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>우리가 선을 행하되 낙심하지 말지니 포기하지 아니하면 때가 이르매 거두리라 그러므로 우리는 기회 있는 대로 모든 이에게 착한 일을 하되 더욱 믿음의 가정들에게 할지니라</t>
+        </is>
+      </c>
       <c r="J73" s="7">
         <f>IF(I73="","",LEN(SUBSTITUTE(I73," ","")))</f>
         <v/>
@@ -4208,8 +5249,18 @@
         <f>IF(I73="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L73" s="10" t="inlineStr"/>
-      <c r="M73" s="10" t="inlineStr"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="14" t="inlineStr">
+        <is>
+          <t>우리가 선을 행하되 낙심하지 말지니 피곤하지 아니하면 때가 이르매 거두리라 그러므로 우리는 기회 있는대로 모든 이에게 착한 일을 하되 더욱 믿음의 가정들에게 할지니라</t>
+        </is>
+      </c>
+      <c r="O73" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="7" t="n">
@@ -4248,7 +5299,11 @@
           <t>마태복음 5장 16절</t>
         </is>
       </c>
-      <c r="I74" s="10" t="inlineStr"/>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>이같이 너희 빛이 사람 앞에 비치게 하여 그들로 너희 착한 행실을 보고 하늘에 계신 너희 아버지께 영광을 돌리게 하라</t>
+        </is>
+      </c>
       <c r="J74" s="7">
         <f>IF(I74="","",LEN(SUBSTITUTE(I74," ","")))</f>
         <v/>
@@ -4257,20 +5312,30 @@
         <f>IF(I74="","본문 필요","")</f>
         <v/>
       </c>
-      <c r="L74" s="10" t="inlineStr"/>
-      <c r="M74" s="10" t="inlineStr"/>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="14" t="inlineStr">
+        <is>
+          <t>이같이 너희 빛을 사람 앞에 비취게 하여 저희로 너희 착한 행실을 보고 하늘에 계신 너희 아버지께 영광을 돌리게 하라</t>
+        </is>
+      </c>
+      <c r="O74" s="16" t="inlineStr">
+        <is>
+          <t>바뀜</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E2:E74">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEN(TRIM(E2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I2:I74">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEN(TRIM(I2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E74">
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>LEN(TRIM(E2))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>